--- a/partner_results/hsh/ClassMissingGermanDefinition_hsh.xlsx
+++ b/partner_results/hsh/ClassMissingGermanDefinition_hsh.xlsx
@@ -446,22 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tire-building machine [hsh]</t>
+          <t>operator [hsh]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>device</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Marvin Auf der Landwehr</t>
-        </is>
-      </c>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A machine that assembles all components and semi-finished products to produce a tire. Constitutes an entity sub-group of the machine entity.</t>
+          <t>A person who operates a machine entity unit in the system under investigation. Constitutes an entity of the human resource and the production cost group.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -469,12 +465,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>banbury mixer [hsh]</t>
+          <t>finished product [hsh]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -484,7 +480,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A machine that mixes polymers and additives in the manufacture of plastic and rubber products. Constitutes an entity sub-group of the machine entity.</t>
+          <t>The product that emerges at the end of the production process of the system under study.  Constitutes an entity in the material cost, production cost, and waste management cost group.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -492,22 +488,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cost [hsh]</t>
+          <t>warehouse clerk [hsh]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>information content entity</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Marvin Auf der Landwehr</t>
-        </is>
-      </c>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cumulative expression for the value of all costs groups within the system under study</t>
+          <t>A person who handles a company's incoming and outgoing raw materials, semi-finished prodcuts as well as finished products, and who manages stocks in the system under investigation. Constitutes an entity of the human ressource and the storage cost group.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -515,12 +507,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>reinforcing material [hsh]</t>
+          <t>cost group [hsh]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -530,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Material that is used to support the structure of rubber-based products (e.g., steel cords). Constitutes an entity subgroup of the raw material entity.</t>
+          <t>Cumulative expression for the value of overarching entity groups (e.g., human ressource, maintenance) within the system under study</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -538,12 +530,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>energy consumption [hsh]</t>
+          <t>banbury mixer [hsh]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>extensive quality</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -553,7 +545,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The amount of electricity (kw/h) that is consumed by all entities in the system under investigation. Constitutes a factor of the energy cost, storage cost and production cost group.</t>
+          <t>A machine that mixes polymers and additives in the manufacture of plastic and rubber products. Constitutes an entity sub-group of the machine entity.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -561,18 +553,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>warehouse clerk [hsh]</t>
+          <t>tire-building machine [hsh]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Marvin Auf der Landwehr</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A person who handles a company's incoming and outgoing raw materials, semi-finished prodcuts as well as finished products, and who manages stocks in the system under investigation. Constitutes an entity of the human ressource and the storage cost group.</t>
+          <t>A machine that assembles all components and semi-finished products to produce a tire. Constitutes an entity sub-group of the machine entity.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -580,12 +576,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>synthetic rubber [hsh]</t>
+          <t>natural rubber [hsh]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rubber particle [chebi]</t>
+          <t>mixture [chebi]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +591,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Any of several substances similar to natural rubber in properties and uses, produced synthetically. Constitutes an entity sub-group of the raw material entity.</t>
+          <t>An elastic material obtained from the latex sap of trees. Constitutes an entity sub-group of the raw material entity.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -626,12 +622,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cost group [hsh]</t>
+          <t>material cost [hsh]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>cost [ncit]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -641,7 +637,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cumulative expression for the value of overarching entity groups (e.g., human ressource, maintenance) within the system under study</t>
+          <t>A cost group for all cost values occuring from entity sub-groups in the material cost group and the associated factors</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -649,7 +645,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quality inspector [hsh]</t>
+          <t>supervisor [hsh]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -660,7 +656,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A person who monitors the quality of incoming and outgoing products or materials in the system under investigation. Constitutes an entity of the human ressource and the production cost group.</t>
+          <t>A person who supervises and coordinates the work of employees who set up and operate machine entity units in the system under investigation. Constitutes an entity of the human ressource and the production cost group.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -668,18 +664,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>operator [hsh]</t>
+          <t>energy cost [hsh]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>cost [ncit]</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marvin Auf der Landwehr</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A person who operates a machine entity unit in the system under investigation. Constitutes an entity of the human resource and the production cost group.</t>
+          <t>A cost group for all cost values occuring from entity sub-groups in the energy cost group and the associated factors</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -687,12 +687,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>finished product [hsh]</t>
+          <t>filling material [hsh]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>chemical substance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>The product that emerges at the end of the production process of the system under study.  Constitutes an entity in the material cost, production cost, and waste management cost group.</t>
+          <t>Material that is required to manipulate the properties of rubber products. Constitutes an entity sub-group of the raw material entity.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -710,22 +710,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tool [hsh]</t>
+          <t>quality inspector [hsh]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>device</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Marvin Auf der Landwehr</t>
-        </is>
-      </c>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>An object shaped for repair and installation purposes, with the help of which something is processed or manufactured.Constitutes an entity sub-group of the wear parts entity.</t>
+          <t>A person who monitors the quality of incoming and outgoing products or materials in the system under investigation. Constitutes an entity of the human ressource and the production cost group.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -733,12 +729,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>material cost [hsh]</t>
+          <t>calandar [hsh]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cost [ncit]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -748,7 +744,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A cost group for all cost values occuring from entity sub-groups in the material cost group and the associated factors</t>
+          <t>A machine that combines a series of hard pressure rollers used to finish or smooth a sheet of rubber material. Constitutes an entity sub-group of the machine entity.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -756,7 +752,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>throughput [hsh]</t>
+          <t>cost [hsh]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -771,7 +767,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The amount of raw materials, semi-finished products or finished products passing through a machine entity in the time X in the system under investigation.</t>
+          <t>Cumulative expression for the value of all costs groups within the system under study</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -779,12 +775,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>filling material [hsh]</t>
+          <t>energy consumption [hsh]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>extensive quality</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -794,7 +790,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Material that is required to manipulate the properties of rubber products. Constitutes an entity sub-group of the raw material entity.</t>
+          <t>The amount of electricity (kw/h) that is consumed by all entities in the system under investigation. Constitutes a factor of the energy cost, storage cost and production cost group.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -802,12 +798,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>natural rubber [hsh]</t>
+          <t>reinforcing material [hsh]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mixture [chebi]</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -817,7 +813,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>An elastic material obtained from the latex sap of trees. Constitutes an entity sub-group of the raw material entity.</t>
+          <t>Material that is used to support the structure of rubber-based products (e.g., steel cords). Constitutes an entity subgroup of the raw material entity.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -825,7 +821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>semi-finished product [hsh]</t>
+          <t>operational assistant [hsh]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -833,14 +829,10 @@
           <t>role</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Marvin Auf der Landwehr</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Processed raw materials that are not used for final consumption but as input for the production of finished goods in the system under investigation. Constitutes an entity in the material cost and waste management cost group.</t>
+          <t>A person who supports an operator in the system under investigation. Constitutes an entity of the human ressource and the production cost group.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -848,12 +840,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>raw material [hsh]</t>
+          <t>synthetic rubber [hsh]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>rubber particle [chebi]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -863,7 +855,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>The basic materials from which a finished product is made in the system under investigation. Constitutes an entity in the material cost and waste management cost group.</t>
+          <t>Any of several substances similar to natural rubber in properties and uses, produced synthetically. Constitutes an entity sub-group of the raw material entity.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -871,7 +863,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>supervisor [hsh]</t>
+          <t>semi-finished product [hsh]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -879,10 +871,14 @@
           <t>role</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marvin Auf der Landwehr</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A person who supervises and coordinates the work of employees who set up and operate machine entity units in the system under investigation. Constitutes an entity of the human ressource and the production cost group.</t>
+          <t>Processed raw materials that are not used for final consumption but as input for the production of finished goods in the system under investigation. Constitutes an entity in the material cost and waste management cost group.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -890,18 +886,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>operational assistant [hsh]</t>
+          <t>throughput [hsh]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>information content entity</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Marvin Auf der Landwehr</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A person who supports an operator in the system under investigation. Constitutes an entity of the human ressource and the production cost group.</t>
+          <t>The amount of raw materials, semi-finished products or finished products passing through a machine entity in the time X in the system under investigation.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -909,12 +909,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>energy cost [hsh]</t>
+          <t>raw material [hsh]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cost [ncit]</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A cost group for all cost values occuring from entity sub-groups in the energy cost group and the associated factors</t>
+          <t>The basic materials from which a finished product is made in the system under investigation. Constitutes an entity in the material cost and waste management cost group.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -932,7 +932,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>calandar [hsh]</t>
+          <t>tool [hsh]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A machine that combines a series of hard pressure rollers used to finish or smooth a sheet of rubber material. Constitutes an entity sub-group of the machine entity.</t>
+          <t>An object shaped for repair and installation purposes, with the help of which something is processed or manufactured.Constitutes an entity sub-group of the wear parts entity.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
